--- a/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-FRM-02_bakim_is_emri_ve_makine_gecmis_karti.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-FRM-02_bakim_is_emri_ve_makine_gecmis_karti.xlsx
@@ -941,7 +941,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Bakım İş Emri ve Makine Geçmiş Kartı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Bakım iş emri ve geçmiş kartına olay, müdahale, parça, doğrulama ve teslim kayıtları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1117,7 +1118,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Bakım İş Emri ve Makine Geçmiş Kartı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Bakım iş emri ve geçmiş kartına olay, müdahale, parça, doğrulama ve teslim kayıtları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>